--- a/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="449">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,16 +316,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -451,7 +451,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -538,10 +538,10 @@
 </t>
   </si>
   <si>
-    <t>ビジネス識別子 / Business identifier</t>
-  </si>
-  <si>
-    <t>この予防接種記録に割り当てられた一意の識別子。 / A unique identifier assigned to this immunization record.</t>
+    <t>ビジネスidentifier / Business identifier</t>
+  </si>
+  <si>
+    <t>この予防接種記録に割り当てられた一意のidentifier。 / A unique identifier assigned to this immunization record.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -939,17 +939,10 @@
     <t>ワクチン製剤が接種された量</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+    <t>RXA-6 / RXA-7</t>
+  </si>
+  <si>
+    <t>.doseQuantity</t>
   </si>
   <si>
     <t>Immunization.performer</t>
@@ -1169,7 +1162,7 @@
     <t>ワクチンを接種するときに患者（あるいは保護者）に提示された教材。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 imm-1:DocumentTypeまたは参照の1つが存在するものとします / One of documentType or reference SHALL be present {documentType.exists() or reference.exists()}</t>
   </si>
   <si>
@@ -1185,10 +1178,10 @@
     <t>Immunization.education.documentType</t>
   </si>
   <si>
-    <t>教育資料文書識別子 / Educational material document identifier</t>
-  </si>
-  <si>
-    <t>患者に提示された材料の識別子。 / Identifier of the material presented to the patient.</t>
+    <t>教育資料文書identifier / Educational material document identifier</t>
+  </si>
+  <si>
+    <t>患者に提示された材料のidentifier。 / Identifier of the material presented to the patient.</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 69764-9</t>
@@ -5168,9 +5161,7 @@
       <c r="M30" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>297</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5228,19 +5219,19 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
@@ -5251,10 +5242,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5277,13 +5268,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5334,7 +5325,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5349,13 +5340,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
@@ -5366,10 +5357,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5395,10 +5386,10 @@
         <v>266</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5449,7 +5440,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5470,7 +5461,7 @@
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>79</v>
@@ -5481,10 +5472,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5510,10 +5501,10 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>162</v>
@@ -5566,7 +5557,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5587,7 +5578,7 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
@@ -5598,14 +5589,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5627,10 +5618,10 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>162</v>
@@ -5685,7 +5676,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5717,10 +5708,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5746,10 +5737,10 @@
         <v>184</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5776,14 +5767,14 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y35" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5800,7 +5791,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5815,13 +5806,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5832,10 +5823,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5858,16 +5849,16 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5917,7 +5908,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -5932,16 +5923,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -5949,10 +5940,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5975,13 +5966,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6032,7 +6023,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6047,13 +6038,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6064,10 +6055,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6093,10 +6084,10 @@
         <v>184</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6126,10 +6117,10 @@
         <v>188</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6147,7 +6138,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6162,13 +6153,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6179,10 +6170,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6205,13 +6196,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6262,7 +6253,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6277,7 +6268,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -6294,10 +6285,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6323,20 +6314,20 @@
         <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>79</v>
@@ -6381,7 +6372,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6399,7 +6390,7 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>133</v>
@@ -6413,10 +6404,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6442,10 +6433,10 @@
         <v>184</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6475,10 +6466,10 @@
         <v>188</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6496,7 +6487,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6528,10 +6519,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6554,13 +6545,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6611,7 +6602,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6623,7 +6614,7 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6643,10 +6634,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6672,10 +6663,10 @@
         <v>266</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6726,7 +6717,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6747,7 +6738,7 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6758,10 +6749,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6787,10 +6778,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>162</v>
@@ -6843,7 +6834,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6864,7 +6855,7 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6875,14 +6866,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6904,10 +6895,10 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>162</v>
@@ -6962,7 +6953,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6994,10 +6985,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7023,10 +7014,10 @@
         <v>266</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7077,7 +7068,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7095,7 +7086,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>133</v>
@@ -7109,10 +7100,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7138,10 +7129,10 @@
         <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7192,7 +7183,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7224,10 +7215,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7253,10 +7244,10 @@
         <v>230</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7307,7 +7298,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7325,7 +7316,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>133</v>
@@ -7339,10 +7330,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7368,10 +7359,10 @@
         <v>230</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7422,7 +7413,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7440,7 +7431,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>133</v>
@@ -7454,10 +7445,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7483,10 +7474,10 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7516,10 +7507,10 @@
         <v>188</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7537,7 +7528,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7555,7 +7546,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>133</v>
@@ -7569,10 +7560,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7598,10 +7589,10 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7631,10 +7622,10 @@
         <v>188</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7652,7 +7643,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7684,10 +7675,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7710,16 +7701,16 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7769,7 +7760,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7787,10 +7778,10 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -7801,10 +7792,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7830,10 +7821,10 @@
         <v>266</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7884,7 +7875,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7905,7 +7896,7 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
@@ -7916,10 +7907,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7945,10 +7936,10 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>162</v>
@@ -8001,7 +7992,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8022,7 +8013,7 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8033,14 +8024,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8062,10 +8053,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>162</v>
@@ -8120,7 +8111,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8152,10 +8143,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8181,10 +8172,10 @@
         <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8235,7 +8226,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8253,7 +8244,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>226</v>
@@ -8267,10 +8258,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8293,13 +8284,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8350,7 +8341,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8368,10 +8359,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
@@ -8382,10 +8373,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8411,10 +8402,10 @@
         <v>236</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8465,7 +8456,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8483,10 +8474,10 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -8497,10 +8488,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8523,13 +8514,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8580,7 +8571,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8612,10 +8603,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8641,10 +8632,10 @@
         <v>266</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8695,7 +8686,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8716,7 +8707,7 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
@@ -8727,10 +8718,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8756,10 +8747,10 @@
         <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>162</v>
@@ -8812,7 +8803,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8833,7 +8824,7 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>79</v>
@@ -8844,14 +8835,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8873,10 +8864,10 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>162</v>
@@ -8931,7 +8922,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8963,10 +8954,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8992,10 +8983,10 @@
         <v>266</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9046,7 +9037,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9078,10 +9069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9104,13 +9095,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9161,7 +9152,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9193,10 +9184,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9222,10 +9213,10 @@
         <v>184</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9255,10 +9246,10 @@
         <v>188</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -9276,7 +9267,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9308,10 +9299,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9334,16 +9325,16 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9393,7 +9384,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>90</v>
@@ -9425,10 +9416,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9451,16 +9442,16 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9510,7 +9501,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="448">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このプロファイルはImmunizationリソースに対して日本での予防接種データを送受信するための制約を加えたものである。</t>
+    <t>このプロファイルはImmunizationリソースに対して日本での予防接種情報を送受信するための制約と拡張を加えたものである。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -268,11 +268,11 @@
     <t>予防接種</t>
   </si>
   <si>
-    <t>ワクチンを接種したときの記録，あるいは予防接種について患者や医療従事者などが報告した記録。</t>
+    <t>予防接種時の記録，あるいは予防接種について患者や医療従事者などが報告した記録。</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -559,7 +559,7 @@
     <t>Immunization.status</t>
   </si>
   <si>
-    <t>完了|エラーに入った|まだ完成してない / completed | entered-in-error | not-done</t>
+    <t>完了 | エラー入力 | 未完了 / completed | entered-in-error | not-done</t>
   </si>
   <si>
     <t>予防接種記録の現在の状態を示すコード</t>
@@ -803,7 +803,7 @@
     <t>ワクチンを接種した場所</t>
   </si>
   <si>
-    <t>接種医療機関。ワクチン接種がどこで実施されたかを表す。サービスが提供された場所。摂取された身体部位ではない。</t>
+    <t>接種医療機関。ワクチン接種がどこで実施されたかを表す。サービスが提供された場所。接種された身体部位ではない。</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -887,10 +887,7 @@
     <t>ワクチンが接種された身体部位</t>
   </si>
   <si>
-    <t>ワクチンが投与されたサイト。 / The site at which the vaccine was administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1043,7 +1040,7 @@
 </t>
   </si>
   <si>
-    <t>演奏していた個人または組織 / Individual or organization who was performing</t>
+    <t>実施・撮影していた個人または組織 / Individual or organization who was performing</t>
   </si>
   <si>
     <t>アクションを実行した開業医または組織。 / The practitioner or organization who performed the action.</t>
@@ -1241,7 +1238,7 @@
     <t>Immunization.fundingSource</t>
   </si>
   <si>
-    <t>ワクチン接種計画のの資金源</t>
+    <t>ワクチン接種計画の資金源</t>
   </si>
   <si>
     <t>ワクチンが実際に接種されるときの資金源を示す。これは患者適格性（たとえば，公的に購入されたワクチンには適格性があるが，在庫の問題で私的資金で購入されたワクチンを投与するような場合）とは異なることがある。</t>
@@ -1388,7 +1385,7 @@
 string</t>
   </si>
   <si>
-    <t>シリーズ内の用量数 / Dose number within series</t>
+    <t>シリーズ内の接種回数 / Dose number within series</t>
   </si>
   <si>
     <t>シリーズの名目上の位置。 / Nominal position in a series.</t>
@@ -1735,7 +1732,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.9296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.4765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -4956,13 +4953,11 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y28" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4998,24 +4993,24 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5041,10 +5036,10 @@
         <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5074,11 +5069,11 @@
         <v>188</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5095,7 +5090,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5113,24 +5108,24 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5153,13 +5148,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5210,7 +5205,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5228,10 +5223,10 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
@@ -5242,10 +5237,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5268,13 +5263,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5325,7 +5320,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5340,13 +5335,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
@@ -5357,10 +5352,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5386,10 +5381,10 @@
         <v>266</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5440,7 +5435,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5461,7 +5456,7 @@
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>79</v>
@@ -5472,10 +5467,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5501,10 +5496,10 @@
         <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>162</v>
@@ -5557,7 +5552,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5578,7 +5573,7 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>79</v>
@@ -5589,14 +5584,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5618,10 +5613,10 @@
         <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>162</v>
@@ -5676,7 +5671,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5708,10 +5703,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5737,10 +5732,10 @@
         <v>184</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5767,14 +5762,14 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Y35" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y35" t="s" s="2">
+      <c r="Z35" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5791,7 +5786,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5806,13 +5801,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5823,10 +5818,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5849,16 +5844,16 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5908,7 +5903,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -5923,16 +5918,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -5940,10 +5935,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5966,13 +5961,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6023,7 +6018,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6038,13 +6033,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6055,10 +6050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6084,10 +6079,10 @@
         <v>184</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6117,11 +6112,11 @@
         <v>188</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6138,7 +6133,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6153,13 +6148,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6170,10 +6165,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6196,13 +6191,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6253,7 +6248,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6268,7 +6263,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -6285,10 +6280,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6314,20 +6309,20 @@
         <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>79</v>
@@ -6372,7 +6367,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6390,7 +6385,7 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>133</v>
@@ -6404,10 +6399,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6433,10 +6428,10 @@
         <v>184</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6466,11 +6461,11 @@
         <v>188</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6487,7 +6482,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6519,10 +6514,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6545,13 +6540,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6602,7 +6597,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6614,7 +6609,7 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6634,10 +6629,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6663,10 +6658,10 @@
         <v>266</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6717,7 +6712,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6738,7 +6733,7 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6749,10 +6744,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6778,10 +6773,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>162</v>
@@ -6834,7 +6829,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6855,7 +6850,7 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6866,14 +6861,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6895,10 +6890,10 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>162</v>
@@ -6953,7 +6948,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6985,10 +6980,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7014,10 +7009,10 @@
         <v>266</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7068,7 +7063,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7086,7 +7081,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>133</v>
@@ -7100,10 +7095,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7129,10 +7124,10 @@
         <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7183,7 +7178,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7215,10 +7210,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7244,10 +7239,10 @@
         <v>230</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7298,7 +7293,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7316,7 +7311,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>133</v>
@@ -7330,10 +7325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7359,10 +7354,10 @@
         <v>230</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7413,7 +7408,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7431,7 +7426,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>133</v>
@@ -7445,10 +7440,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7474,10 +7469,10 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7507,11 +7502,11 @@
         <v>188</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7528,7 +7523,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7546,7 +7541,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>133</v>
@@ -7560,10 +7555,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7589,10 +7584,10 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7622,11 +7617,11 @@
         <v>188</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7643,7 +7638,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7675,10 +7670,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7701,16 +7696,16 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7760,7 +7755,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7778,10 +7773,10 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>79</v>
@@ -7792,10 +7787,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7821,10 +7816,10 @@
         <v>266</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7875,7 +7870,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7896,7 +7891,7 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>79</v>
@@ -7907,10 +7902,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7936,10 +7931,10 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>162</v>
@@ -7992,7 +7987,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8013,7 +8008,7 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8024,14 +8019,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8053,10 +8048,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>162</v>
@@ -8111,7 +8106,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8143,10 +8138,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8172,10 +8167,10 @@
         <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8226,7 +8221,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8244,7 +8239,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>226</v>
@@ -8258,10 +8253,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8284,13 +8279,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8341,7 +8336,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8359,10 +8354,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
@@ -8373,10 +8368,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8402,10 +8397,10 @@
         <v>236</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8456,7 +8451,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8474,10 +8469,10 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>79</v>
@@ -8488,10 +8483,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8514,13 +8509,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8571,7 +8566,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8603,10 +8598,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8632,10 +8627,10 @@
         <v>266</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8686,7 +8681,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8707,7 +8702,7 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
@@ -8718,10 +8713,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8747,10 +8742,10 @@
         <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>162</v>
@@ -8803,7 +8798,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8824,7 +8819,7 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>79</v>
@@ -8835,14 +8830,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8864,10 +8859,10 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>162</v>
@@ -8922,7 +8917,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8954,10 +8949,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8983,10 +8978,10 @@
         <v>266</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9037,7 +9032,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9069,10 +9064,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9095,13 +9090,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9152,7 +9147,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9184,10 +9179,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9213,10 +9208,10 @@
         <v>184</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9246,11 +9241,11 @@
         <v>188</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Z65" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
       </c>
@@ -9267,7 +9262,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9299,10 +9294,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9325,16 +9320,16 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9384,7 +9379,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>90</v>
@@ -9416,10 +9411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9442,16 +9437,16 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="N67" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9501,7 +9496,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>

--- a/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
@@ -1707,17 +1707,17 @@
   <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.78125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.78125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.88671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.25" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.25" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.05078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="176.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1726,27 +1726,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.9296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.02734375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="43.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.81640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.46484375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="37.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="147.5546875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="236.8828125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="158.05078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="126.50390625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="203.0859375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="135.5" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
@@ -370,7 +370,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -608,7 +608,7 @@
     <t>ワクチンが投与されなかった理由。 / The reason why a vaccine was not administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -787,7 +787,7 @@
     <t>主要なソースからのものではないレコードのデータのソース。 / The source of the data for a record which is not from a primary source.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-origin</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-origin|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=INF].role[classCode=PAT] (this syntax for self-reported) .participation[typeCode=INF].role[classCode=LIC] (this syntax for health care professional) .participation[typeCode=INF].role[classCode=PRS] (this syntax for family member)</t>
@@ -911,7 +911,7 @@
     <t>ワクチンが投与されたルート。 / The route by which the vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-route|4.0.1</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1024,7 +1024,7 @@
     <t>予防接種イベントで開業医または組織が果たす役割。 / The role a practitioner or organization plays in the immunization event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-function</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1092,7 +1092,7 @@
     <t>ワクチンが投与された理由。 / The reason why a vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1104,7 +1104,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>用量がサブポテントと見なされる理由。 / The reason why a dose is considered to be subpotent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason|4.0.1</t>
   </si>
   <si>
     <t>Immunization.education</t>
@@ -1229,7 +1229,7 @@
     <t>患者の予防接種プログラムの適格性。 / The patient's eligibility for a vaccation program.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility|4.0.1</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 64994-7</t>
@@ -1247,7 +1247,7 @@
     <t>投与されたワクチンの購入に使用される資金源。 / The source of funding used to purchase the vaccine administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source|4.0.1</t>
   </si>
   <si>
     <t>Immunization.reaction</t>
@@ -1292,7 +1292,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1353,7 +1353,7 @@
     <t>Immunization.protocolApplied.authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1375,7 +1375,7 @@
     <t>ワクチン予防可能な疾患用量が投与されています。 / The vaccine preventable disease the dose is being administered for.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease|4.0.1</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>

--- a/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-immunization.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
